--- a/data/후원.xlsx
+++ b/data/후원.xlsx
@@ -77,27 +77,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00E4DCD2"/>
-      </left>
-      <right style="thin">
-        <color rgb="00E4DCD2"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E4DCD2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E4DCD2"/>
-      </bottom>
     </border>
     <border>
       <bottom style="thin">
@@ -108,24 +94,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -492,10 +481,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="112" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,7 +497,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>이 파일 하나로 '후원 안내' 페이지가 만들어집니다. 줄을 고치거나 추가하면 화면도 바뀝니다.</t>
+          <t>이 파일(또는 '홈페이지 편집기')로 후원 페이지가 만들어집니다.</t>
         </is>
       </c>
     </row>
@@ -522,112 +511,70 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 종류(칸) 설명 — 종류에 따라 화면 위치가 정해집니다</t>
+          <t>■ 탭 칸</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  소개    = 맨 위 소개 문구 (내용 칸)</t>
+          <t xml:space="preserve">  비워두면 페이지 공통 영역(맨 위·맨 아래), 이름을 쓰면 그 탭 안에 들어갑니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  계좌    = 후원 계좌 카드. 이름/라벨=은행명, 내용=계좌번호, 아이콘=bank</t>
+          <t xml:space="preserve">  탭 이름을 바꾸면 화면의 탭 이름이 바뀌고, 새 이름을 쓰면 탭이 추가됩니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  예금주  = 계좌 아래 예금주 표시 (내용 칸)</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  방법    = '후원 방법' 카드. 이름/라벨=방법명, 내용=설명, 아이콘=아래 목록 중</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>■ 종류 (탭 비움)  소개=맨 위 문구 · 계좌=이름에 은행, 내용에 계좌번호 · 예금주 · 문의=전화번호 · 안내=맨 아래 안내박스</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  종류    = '후원 종류' 카드. 이름/라벨=종류명, 내용=설명, 아이콘=아래 목록 중</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 종류 (탭 있음)  카드 · 절차(이름=단계) · 혜택(이름+내용+아이콘) · 안내(탭 안 안내박스) · 사진(사진 칸=파일명, 캡션)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  혜택    = '후원 혜택' 목록. 이름/라벨=혜택명, 내용=설명, 아이콘=아래 목록 중</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  문의    = 하단 후원 문의 전화번호 (내용 칸)</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 사진 파일은 GitHub data/후원_img/ 폴더에 같은 이름으로 올립니다. (가로 4:3, 2MB 이하, jpg 권장)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  안내    = 맨 아래 주황 안내 박스 (내용 칸)</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>■ 아이콘: phone home meal talk user users clean music health pill walk shield star heart hand gift bread coffee mic mega bell mail book edit camera calendar clock car bus mappin leaf flower sun smile scissors wrench bank card box link receipt check</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>■ 아이콘 목록: bank heart hand card calendar box link receipt gift bell mega phone check</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   (모르면 비워두세요. 하트 아이콘으로 표시됩니다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>■ 게시 : O=보임 / X=숨김</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>■ 줄을 추가하면 그 종류의 항목이 화면에 하나 더 늘어납니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>■ ※ 예금주 이름은 재단 확인 후 정확히 입력해 주세요.</t>
         </is>
       </c>
     </row>
@@ -642,14 +589,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -662,7 +613,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>종류 칸을 클릭해 목록에서 고르세요 · 계좌/방법/종류/혜택은 줄 순서대로 표시됩니다</t>
+          <t>탭 칸이 비면 페이지 공통 영역, 탭 이름을 쓰면 그 탭 안에 들어갑니다. 같은 탭 이름끼리 한 탭으로 묶입니다.</t>
         </is>
       </c>
     </row>
@@ -674,22 +625,42 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
+          <t>탭</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
           <t>종류</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>이름/라벨</t>
-        </is>
-      </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
+          <t>이름·라벨</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>태그</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>아이콘</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>사진</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>캡션</t>
         </is>
       </c>
     </row>
@@ -699,18 +670,22 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>소개</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>여러분의 작은 나눔이 어르신들께는 큰 힘이 됩니다. 지역사회 어르신들이 건강하고 행복한 노후를 보내실 수 있도록 따뜻한 후원의 손길에 함께해 주세요.</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -718,26 +693,30 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>계좌</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>기업은행</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>128-153256-01-011</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>bank</t>
         </is>
       </c>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -745,26 +724,30 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>계좌</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>하나은행</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>793-910046-91005</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>bank</t>
         </is>
       </c>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -772,26 +755,30 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>계좌</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>신협</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>131-022-116603</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>bank</t>
         </is>
       </c>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -799,18 +786,22 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>예금주</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>북원노인종합복지관</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -818,26 +809,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>방법</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>후원 방법</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>카드</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>직접 전달</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>복지관에 직접 방문하여 후원금(품)을 전달하실 수 있습니다.</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>hand</t>
         </is>
       </c>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -845,26 +844,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>방법</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>후원 방법</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>카드</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>계좌 이체</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>위 후원 계좌로 직접 이체하여 후원하실 수 있습니다.</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>card</t>
         </is>
       </c>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -872,26 +879,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>방법</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>후원 방법</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>카드</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>CMS 자동이체</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>매월 지정한 날짜(5·10·20·25일)에 후원금이 자동 출금됩니다. 신청은 후원 문의처로 연락 주세요.</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>calendar</t>
         </is>
       </c>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -899,26 +914,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>종류</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>후원 종류</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>카드</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>일반후원</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>정기 또는 일시로 후원금을 지원하는 후원입니다.</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>heart</t>
         </is>
       </c>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -926,26 +949,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>종류</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>후원 종류</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>카드</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>결연후원</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>후원자와 어르신을 연결하여 지속적으로 지원하는 후원입니다.</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>link</t>
         </is>
       </c>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -953,26 +984,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>종류</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>후원 종류</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>카드</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>물품후원</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>생활용품·식료품 등 필요한 물품을 지원하는 후원입니다.</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>box</t>
         </is>
       </c>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -980,26 +1019,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>후원 혜택</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>혜택</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>연말정산 세제 혜택</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>소득세법 제59조의4·제34조 및 법인세법 제24조에 따라 기부금 세액공제(소득공제) 혜택을 받으실 수 있습니다.</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>receipt</t>
         </is>
       </c>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -1007,26 +1054,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>후원 혜택</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>혜택</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>기관 행사 초청</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>복지관 주요 행사에 후원자님을 초청해 드립니다.</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>gift</t>
         </is>
       </c>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -1034,26 +1089,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>후원 혜택</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>혜택</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>후원 소식 안내</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>후원금이 어떻게 쓰였는지 후원 소식지를 통해 정기적으로 안내해 드립니다.</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>bell</t>
         </is>
       </c>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -1061,26 +1124,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>후원 혜택</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>혜택</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>후원자(단체) 홍보</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>희망하시는 경우 후원자(단체)를 홈페이지 등을 통해 홍보해 드립니다.</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>mega</t>
         </is>
       </c>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -1088,22 +1159,22 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>문의</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>033-747-0516</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -1111,33 +1182,37 @@
           <t>O</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>안내</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>후원금 영수증(기부금 영수증) 발급 및 후원 방법 변경 등 자세한 사항은 후원 문의처로 연락 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="A5:A61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"O,X"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5:B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"소개,계좌,예금주,방법,종류,혜택,문의,안내"</formula1>
+    <dataValidation sqref="C5:C82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"소개,계좌,예금주,문의,안내,카드,절차,혜택,사진"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"bank,heart,hand,card,calendar,box,link,receipt,gift,bell,mega,phone,check"</formula1>
+    <dataValidation sqref="G5:G82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"phone,home,meal,talk,user,users,clean,music,health,pill,walk,shield,star,heart,hand,gift,bread,coffee,mic,mega,bell,mail,book,edit,camera,calendar,clock,car,bus,mappin,leaf,flower,sun,smile,scissors,wrench,bank,card,box,link,receipt,check"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/후원.xlsx
+++ b/data/후원.xlsx
@@ -567,7 +567,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ 아이콘: phone home meal talk user users clean music health pill walk shield star heart hand gift bread coffee mic mega bell mail book edit camera calendar clock car bus mappin leaf flower sun smile scissors wrench bank card box link receipt check</t>
+          <t>■ 아이콘: phone home meal talk user users clean music health pill walk shield star heart hand gift bread coffee mic mega bell mail book edit camera calendar clock car bus mappin leaf flower sun smile scissors wrench bank card box link receipt pin route check</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       <formula1>"소개,계좌,예금주,문의,안내,카드,절차,혜택,사진"</formula1>
     </dataValidation>
     <dataValidation sqref="G5:G82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"phone,home,meal,talk,user,users,clean,music,health,pill,walk,shield,star,heart,hand,gift,bread,coffee,mic,mega,bell,mail,book,edit,camera,calendar,clock,car,bus,mappin,leaf,flower,sun,smile,scissors,wrench,bank,card,box,link,receipt,check"</formula1>
+      <formula1>"phone,home,meal,talk,user,users,clean,music,health,pill,walk,shield,star,heart,hand,gift,bread,coffee,mic,mega,bell,mail,book,edit,camera,calendar,clock,car,bus,mappin,leaf,flower,sun,smile,scissors,wrench,bank,card,box,link,receipt,pin,route,check"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
